--- a/dashboard-embarazo-matronas-chile/Embarazo_Matronas_BaseDatos.xlsx
+++ b/dashboard-embarazo-matronas-chile/Embarazo_Matronas_BaseDatos.xlsx
@@ -22,7 +22,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hallazgos" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AdolLargo" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="InfantilLargo" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuentes" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPILargo" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SimColegios" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SimAcceso" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SimEfecto" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SimCondon" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SimIndicadores" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SimSupuestos" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuentes" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -75,11 +83,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -236,12 +247,67 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="Fuentes" displayName="Fuentes" ref="A1:C51" headerRowCount="1">
-  <autoFilter ref="A1:C51"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="KPI" displayName="KPI" ref="A1:I11" headerRowCount="1">
+  <autoFilter ref="A1:I11"/>
+  <tableColumns count="9">
+    <tableColumn id="1" name="Orden"/>
+    <tableColumn id="2" name="Area"/>
+    <tableColumn id="3" name="KPI"/>
+    <tableColumn id="4" name="Valor"/>
+    <tableColumn id="5" name="Formula"/>
+    <tableColumn id="6" name="QueMide"/>
+    <tableColumn id="7" name="PorQue"/>
+    <tableColumn id="8" name="Meta"/>
+    <tableColumn id="9" name="FuenteID"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="KPILargo" displayName="KPILargo" ref="A1:E71" headerRowCount="1">
+  <autoFilter ref="A1:E71"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="OrdenKPI"/>
+    <tableColumn id="2" name="KPI"/>
+    <tableColumn id="3" name="OrdenCampo"/>
+    <tableColumn id="4" name="Campo"/>
+    <tableColumn id="5" name="Valor"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="SimColegios" displayName="SimColegios" ref="A1:B12" headerRowCount="1">
+  <autoFilter ref="A1:B12"/>
+  <tableColumns count="2">
+    <tableColumn id="1" name="Porcentaje"/>
+    <tableColumn id="2" name="Orden"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="SimAcceso" displayName="SimAcceso" ref="A1:C3" headerRowCount="1">
+  <autoFilter ref="A1:C3"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="FuenteID"/>
-    <tableColumn id="2" name="Referencia"/>
-    <tableColumn id="3" name="URL"/>
+    <tableColumn id="1" name="Opcion"/>
+    <tableColumn id="2" name="Valor"/>
+    <tableColumn id="3" name="Orden"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="SimEfecto" displayName="SimEfecto" ref="A1:C3" headerRowCount="1">
+  <autoFilter ref="A1:C3"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="Escenario"/>
+    <tableColumn id="2" name="Porcentaje"/>
+    <tableColumn id="3" name="Orden"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
@@ -256,6 +322,56 @@
     <tableColumn id="3" name="Periodo"/>
     <tableColumn id="4" name="Poblacion"/>
     <tableColumn id="5" name="FuenteID"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="SimCondon" displayName="SimCondon" ref="A1:B6" headerRowCount="1">
+  <autoFilter ref="A1:B6"/>
+  <tableColumns count="2">
+    <tableColumn id="1" name="Puntos"/>
+    <tableColumn id="2" name="Orden"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="SimIndicadores" displayName="SimIndicadores" ref="A1:D4" headerRowCount="1">
+  <autoFilter ref="A1:D4"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="Orden"/>
+    <tableColumn id="2" name="Indicador"/>
+    <tableColumn id="3" name="Base"/>
+    <tableColumn id="4" name="Tipo"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="SimSupuestos" displayName="SimSupuestos" ref="A1:E8" headerRowCount="1">
+  <autoFilter ref="A1:E8"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Orden"/>
+    <tableColumn id="2" name="Supuesto"/>
+    <tableColumn id="3" name="Valor"/>
+    <tableColumn id="4" name="PorQue"/>
+    <tableColumn id="5" name="FuenteID"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="Fuentes" displayName="Fuentes" ref="A1:C53" headerRowCount="1">
+  <autoFilter ref="A1:C51"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="FuenteID"/>
+    <tableColumn id="2" name="Referencia"/>
+    <tableColumn id="3" name="URL"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
@@ -650,9 +766,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -2082,879 +2196,2362 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
+          <t>Orden</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>KPI</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>QueMide</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>PorQue</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
           <t>FuenteID</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Embarazo adolescente</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Tasa específica de fecundidad de 15 a 19 años</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>8,3 por 1.000 (2025)</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Nacidos vivos de madres de 15 a 19 ÷ mujeres de 15 a 19 × 1.000</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Cuántos nacimientos hay por cada 1.000 adolescentes</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Indicador ODS 3.7.2; refleja acceso a educación sexual y anticoncepción</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Seguir bajando (23,2 en 2018)</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>E4;E8</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Embarazo adolescente</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Nacidos vivos de madres de 10 a 14 años</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>146 (2025)</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Número de nacidos vivos de madres de 10 a 14 años en el año</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Embarazos en niñas</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Todo embarazo bajo 14 años es una alerta de protección y posible abuso</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Cero</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>E8</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Embarazo adolescente</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Uso de anticonceptivo en la primera relación</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>86,6% (2022)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Jóvenes que usaron algún método en su inicio sexual ÷ jóvenes con inicio sexual × 100</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Protección desde la primera relación</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Es el momento de mayor riesgo de embarazo no planificado e ITS</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Acercarse al 100%</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>E11</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Embarazo adolescente</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Necesidad insatisfecha de planificación familiar</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>6% (2019)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Mujeres que no quieren embarazarse y no usan método ÷ mujeres en edad fértil × 100</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Brecha entre el deseo de no embarazarse y el acceso a un método</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Relacionado con el ODS 3.7.1: mide el acceso real a anticoncepción</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Lo más bajo posible</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>E13</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Matronas en Chile</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Densidad de matronas</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>8,7 por 10.000 habitantes (2022)</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Matronas inscritas ÷ población × 10.000</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Disponibilidad de matronas para la población</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>La OMS usa la densidad de personal de salud para estimar si alcanza para cubrir la atención</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>E16;E13</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Matronas en Chile</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Crecimiento de matronas inscritas</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>+61% (2019–2025)</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>(Inscritas 2025 − inscritas 2019) ÷ inscritas 2019 × 100</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Cuánto crece la fuerza de trabajo</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Chile forma más matronas de las que contrata: el desafío son los cupos</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>E16;E17</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Mortalidad materna y neonatal</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Razón de mortalidad materna (RMM)</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>10 por 100.000 nacidos vivos (ONU 2023)</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Muertes maternas ÷ nacidos vivos × 100.000</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Riesgo de morir por causas del embarazo, parto o puerperio</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Indicador ODS 3.1.1: refleja acceso y calidad de la atención materna</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>ODS: &lt; 70 (mundo); Chile ya la cumple</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>E24;E23</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Mortalidad materna y neonatal</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de mortalidad infantil</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>5,9 por 1.000 nacidos vivos (2025)</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Defunciones de menores de 1 año ÷ nacidos vivos × 1.000</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Riesgo de morir antes del primer año</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Es uno de los mejores reflejos del nivel de salud de un país</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Mantener bajo 7</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>E8</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Mortalidad materna y neonatal</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de mortalidad neonatal</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>4,8 por 1.000 nacidos vivos (2023)</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Defunciones de 0 a 27 días ÷ nacidos vivos × 1.000</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Riesgo de morir en el primer mes</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Indicador ODS 3.2.2: depende del control prenatal, el parto y la atención del recién nacido</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>ODS: ≤ 12</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>E28</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Lo que dice la evidencia</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Riesgo relativo de parto prematuro con continuidad de matrona</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>RR 0,76 (−24%)</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Riesgo en el grupo con continuidad de matrona ÷ riesgo en el grupo con atención habitual</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Cuánto cambia el riesgo con el modelo de matronas</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Un RR menor que 1 indica protección; viene de ensayos clínicos (Cochrane)</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>E33</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E71"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>OrdenKPI</t>
+        </is>
+      </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Referencia</t>
+          <t>KPI</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>URL</t>
+          <t>OrdenCampo</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Campo</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Valor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>E1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>MINSAL, Actualización de la situación de salud de adolescentes (2021).</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>https://diprece.minsal.cl/wp-content/uploads/2021/06/ACTUALIZACION-SITUACION-DE-SALUD-DE-ADOLESCENTES-PROGRAMA-NACIONAL-DE-SALUD-INTEGRAL-DE-ADOLESCENTES-Y-JOVENES.pdf</t>
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Tasa específica de fecundidad de 15 a 19 años</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Valor en Chile</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>8,3 por 1.000 (2025)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>E2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>INE, Enfoque estadístico maternidad y paternidad (2017).</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://www.ine.gob.cl/docs/default-source/genero/documentos-de-an%C3%A1lisis/documentos/enfoque-maternidad-paternidad-2017.pdf</t>
+      <c r="A3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Tasa específica de fecundidad de 15 a 19 años</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Cómo se calcula</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Nacidos vivos de madres de 15 a 19 ÷ mujeres de 15 a 19 × 1.000</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>E3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>INE vía Emol, cifras de maternidad en Chile (2020).</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.emol.com/noticias/Economia/2020/05/09/985650/Cifras-maternidad-en-Chile.html</t>
+      <c r="A4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Tasa específica de fecundidad de 15 a 19 años</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Qué evalúa</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Cuántos nacimientos hay por cada 1.000 adolescentes</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>E4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>INE, nacimientos 2018 (nota de prensa, 2021).</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://www.ine.gob.cl/sala-de-prensa/prensa/general/noticia/2021/01/11/nacimientos-de-madres-extranjeras-crecen-y-alcanzan-el-14-en-chile</t>
+      <c r="A5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Tasa específica de fecundidad de 15 a 19 años</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Por qué importa</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Indicador ODS 3.7.2; refleja acceso a educación sexual y anticoncepción</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>E5</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>La Tercera, embarazo adolescente en su cifra más baja (2024).</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.latercera.com/que-pasa/noticia/uso-de-anticonceptivos-llevan-al-embarazo-adolescente-a-la-cifra-mas-baja-desde-que-hay-registros/H5QUT6YRKNH2VDXD7LV6BPYH7Y/</t>
+      <c r="A6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Tasa específica de fecundidad de 15 a 19 años</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Meta o referencia</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Seguir bajando (23,2 en 2018)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>E6</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>INE, Estadísticas vitales: fecundidad en Chile (17-03-2025).</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.ine.gob.cl/sala-de-prensa/prensa/general/noticia/2025/03/17/estad%C3%ADsticas-vitales-fecundidad-en-chile-sigue-bajo-del-nivel-de-reemplazo-generacional</t>
+      <c r="A7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Tasa específica de fecundidad de 15 a 19 años</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Página del tablero</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Embarazo adolescente</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>E7</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>INE, Estadísticas vitales cifras provisionales 2024.</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://www.ine.gob.cl/docs/default-source/nacimientos-matrimonios-y-defunciones/publicaciones-y-anuarios/anuarios-de-estad%C3%ADsticas-vitales/estad%C3%ADsticas-vitales-cifras-provisionales-2024.pdf</t>
+      <c r="A8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Tasa específica de fecundidad de 15 a 19 años</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>E4;E8</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Nacidos vivos de madres de 10 a 14 años</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Valor en Chile</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>146 (2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Nacidos vivos de madres de 10 a 14 años</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Cómo se calcula</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Número de nacidos vivos de madres de 10 a 14 años en el año</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Nacidos vivos de madres de 10 a 14 años</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Qué evalúa</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Embarazos en niñas</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Nacidos vivos de madres de 10 a 14 años</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Por qué importa</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Todo embarazo bajo 14 años es una alerta de protección y posible abuso</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Nacidos vivos de madres de 10 a 14 años</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Meta o referencia</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Cero</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Nacidos vivos de madres de 10 a 14 años</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Página del tablero</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Embarazo adolescente</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Nacidos vivos de madres de 10 a 14 años</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>E8</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>INE, Estadísticas vitales cifras provisionales 2025.</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>https://www.ine.gob.cl/docs/default-source/nacimientos-matrimonios-y-defunciones/publicaciones-y-anuarios/anuarios-de-estad%C3%ADsticas-vitales/estad%C3%ADsticas-vitales-cifras-provisionales-2025.pdf</t>
-        </is>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Uso de anticonceptivo en la primera relación</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Valor en Chile</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>86,6% (2022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Uso de anticonceptivo en la primera relación</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Cómo se calcula</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Jóvenes que usaron algún método en su inicio sexual ÷ jóvenes con inicio sexual × 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Uso de anticonceptivo en la primera relación</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Qué evalúa</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Protección desde la primera relación</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Uso de anticonceptivo en la primera relación</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Por qué importa</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Es el momento de mayor riesgo de embarazo no planificado e ITS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Uso de anticonceptivo en la primera relación</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Meta o referencia</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Acercarse al 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Uso de anticonceptivo en la primera relación</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Página del tablero</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Embarazo adolescente</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Uso de anticonceptivo en la primera relación</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>E11</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Necesidad insatisfecha de planificación familiar</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Valor en Chile</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>6% (2019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Necesidad insatisfecha de planificación familiar</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Cómo se calcula</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Mujeres que no quieren embarazarse y no usan método ÷ mujeres en edad fértil × 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Necesidad insatisfecha de planificación familiar</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Qué evalúa</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Brecha entre el deseo de no embarazarse y el acceso a un método</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Necesidad insatisfecha de planificación familiar</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Por qué importa</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Relacionado con el ODS 3.7.1: mide el acceso real a anticoncepción</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Necesidad insatisfecha de planificación familiar</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Meta o referencia</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Lo más bajo posible</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Necesidad insatisfecha de planificación familiar</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Página del tablero</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Embarazo adolescente</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Necesidad insatisfecha de planificación familiar</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>E13</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Densidad de matronas</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Valor en Chile</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>8,7 por 10.000 habitantes (2022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Densidad de matronas</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Cómo se calcula</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Matronas inscritas ÷ población × 10.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Densidad de matronas</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Qué evalúa</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Disponibilidad de matronas para la población</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Densidad de matronas</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Por qué importa</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>La OMS usa la densidad de personal de salud para estimar si alcanza para cubrir la atención</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Densidad de matronas</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Meta o referencia</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Densidad de matronas</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Página del tablero</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Matronas en Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Densidad de matronas</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>E16;E13</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Crecimiento de matronas inscritas</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Valor en Chile</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>+61% (2019–2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Crecimiento de matronas inscritas</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Cómo se calcula</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>(Inscritas 2025 − inscritas 2019) ÷ inscritas 2019 × 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Crecimiento de matronas inscritas</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Qué evalúa</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Cuánto crece la fuerza de trabajo</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Crecimiento de matronas inscritas</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Por qué importa</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Chile forma más matronas de las que contrata: el desafío son los cupos</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Crecimiento de matronas inscritas</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Meta o referencia</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Crecimiento de matronas inscritas</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Página del tablero</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Matronas en Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Crecimiento de matronas inscritas</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>E16;E17</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Razón de mortalidad materna (RMM)</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Valor en Chile</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>10 por 100.000 nacidos vivos (ONU 2023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Razón de mortalidad materna (RMM)</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Cómo se calcula</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Muertes maternas ÷ nacidos vivos × 100.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Razón de mortalidad materna (RMM)</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Qué evalúa</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Riesgo de morir por causas del embarazo, parto o puerperio</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Razón de mortalidad materna (RMM)</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Por qué importa</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Indicador ODS 3.1.1: refleja acceso y calidad de la atención materna</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Razón de mortalidad materna (RMM)</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Meta o referencia</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>ODS: &lt; 70 (mundo); Chile ya la cumple</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Razón de mortalidad materna (RMM)</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Página del tablero</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Mortalidad materna y neonatal</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Razón de mortalidad materna (RMM)</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>E24;E23</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de mortalidad infantil</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Valor en Chile</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>5,9 por 1.000 nacidos vivos (2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de mortalidad infantil</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Cómo se calcula</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Defunciones de menores de 1 año ÷ nacidos vivos × 1.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de mortalidad infantil</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Qué evalúa</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Riesgo de morir antes del primer año</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de mortalidad infantil</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Por qué importa</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Es uno de los mejores reflejos del nivel de salud de un país</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de mortalidad infantil</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Meta o referencia</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Mantener bajo 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de mortalidad infantil</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Página del tablero</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Mortalidad materna y neonatal</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de mortalidad infantil</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>E8</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de mortalidad neonatal</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Valor en Chile</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>4,8 por 1.000 nacidos vivos (2023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de mortalidad neonatal</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Cómo se calcula</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Defunciones de 0 a 27 días ÷ nacidos vivos × 1.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de mortalidad neonatal</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Qué evalúa</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Riesgo de morir en el primer mes</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de mortalidad neonatal</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Por qué importa</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Indicador ODS 3.2.2: depende del control prenatal, el parto y la atención del recién nacido</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de mortalidad neonatal</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Meta o referencia</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>ODS: ≤ 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de mortalidad neonatal</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Página del tablero</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Mortalidad materna y neonatal</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Tasa de mortalidad neonatal</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>E28</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Riesgo relativo de parto prematuro con continuidad de matrona</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Valor en Chile</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>RR 0,76 (−24%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Riesgo relativo de parto prematuro con continuidad de matrona</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Cómo se calcula</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Riesgo en el grupo con continuidad de matrona ÷ riesgo en el grupo con atención habitual</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>Riesgo relativo de parto prematuro con continuidad de matrona</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Qué evalúa</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>Cuánto cambia el riesgo con el modelo de matronas</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Riesgo relativo de parto prematuro con continuidad de matrona</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Por qué importa</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Un RR menor que 1 indica protección; viene de ensayos clínicos (Cochrane)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>Riesgo relativo de parto prematuro con continuidad de matrona</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>Meta o referencia</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Riesgo relativo de parto prematuro con continuidad de matrona</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Página del tablero</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Lo que dice la evidencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>Riesgo relativo de parto prematuro con continuidad de matrona</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>E33</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Porcentaje</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Orden</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>E9</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Intramed: caída del embarazo adolescente en Chile (Rodríguez Vignoli, CEPAL).</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>https://www.intramed.net/content/67057bde57fbbb5669b34e22</t>
-        </is>
+      <c r="A10" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>E10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>CEPAL, Rodríguez Vignoli: fecundidad adolescente en Chile (datos INJUV 2018).</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>https://repositorio.cepal.org/server/api/core/bitstreams/6dd4f6c2-3ace-4da3-a9de-b36f1be56c9f/content</t>
-        </is>
+      <c r="A11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>E11</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>La Tercera Paula: 10.ª Encuesta Nacional de Juventudes INJUV 2022.</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>https://www.latercera.com/paula/mas-tarde-y-las-mujeres-primero-radiografia-al-sexo-adolescente/</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>E12</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>La Tercera: 50% de los embarazos en Chile no son planificados (encuesta 2010).</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>https://www.latercera.com/noticia/50-de-los-embarazos-en-chile-no-son-planificados/</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>E13</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>UNFPA, State of the World's Midwifery 2021: perfil de Chile.</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>https://www.unfpa.org/sites/default/files/sowmy21/en/sowmy-2021-profile-cl.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>E14</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Guttmacher, embarazo no planeado en América Latina y el Caribe (2022).</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>https://www.guttmacher.org/es/infographic/2022/la-tasa-de-embarazo-no-planeado-en-america-latina-y-el-caribe-es-de-69-por-cada</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>E15</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>UNFPA, casi la mitad de los embarazos no son intencionales (SWOP 2022).</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>https://www.unfpa.org/press/nearly-half-all-pregnancies-are-unintended%E2%80%94-global-crisis-says-new-unfpa-report</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>E16</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>MINSAL, Glosa 01 letra d: profesionales inscritos en el RNPI (informe 2023).</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>https://www.minsal.cl/wp-content/uploads/2021/05/Glosa-01-d-Ano-2023.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>E17</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>MINSAL, Glosa 01 letra d (informe 2026, datos a diciembre de 2025).</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>https://www.minsal.cl/wp-content/uploads/2026/07/Glosa-01-letra-d-comun-a-los-capitulos-inciso-04.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>E18</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Clínicas de Chile, Dimensionamiento del sector salud 2022.</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>https://www.clinicasdechile.cl/wp-content/uploads/2023/12/Dimensionamiento-Completo-2022.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>E19</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>MINSAL, Normas Nacionales sobre Regulación de la Fertilidad (2018).</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>https://www.minsal.cl/wp-content/uploads/2015/09/2018.01.30_NORMAS-REGULACION-DE-LA-FERTILIDAD.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>E20</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>UNFPA/OMS/ICM, State of the World's Midwifery 2021.</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>https://unfpa.org/state-worlds-midwifery-2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>E21</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>MINSAL, Espacios Amigables en Ñuble (2025).</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>https://www.minsal.cl/espacios-amigables-se-refuerza-red-de-apoyo-en-salud-para-adolescentes-en-nuble/</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>E22</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Mortalidad materna Chile 2001–2021 (póster congreso UFRO 2023, datos DEIS).</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>https://congreso2023.ufro.cl/images/presentaciones/e-poster/viernes/pantalla7/07-797-Tendencias%20de%20Mortalidad%20Materna.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>E23</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>González et al., Rev Méd Clín Las Condes 2023: mortalidad materna y prematuridad en pandemia (datos DEIS).</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>https://www.elsevier.es/es-revista-revista-medica-clinica-las-condes-202-articulo-aumento-mortalidad-materna-prematuridad-durante-S0716864023000111</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>E24</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>ORAS-CONHU, Sala situacional de mortalidad materna (estimaciones ONU 2023).</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>https://www.orasconhu.org/sites/default/files/file/webfiles/doc/Sala%20Situacional%2014-04-2025%20Mortalidad%20Materna.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>E25</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>OMS, nota descriptiva de mortalidad materna.</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>https://www.who.int/news-room/fact-sheets/detail/maternal-mortality</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>E26</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>INE, Anuario de estadísticas vitales 2018 (síntesis).</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>https://www.ine.gob.cl/docs/default-source/nacimientos-matrimonios-y-defunciones/publicaciones-y-anuarios/s%C3%ADntesis-anuarios-de-estad%C3%ADsticas-vitales/anuario-de-estad%C3%ADsticas-vitales-2018-s%C3%ADntesis.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>E27</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>INE, Anuario de estadísticas vitales 2022.</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>https://www.ine.gob.cl/docs/default-source/nacimientos-matrimonios-y-defunciones/publicaciones-y-anuarios/anuarios-de-estad%C3%ADsticas-vitales/anuario-de-estad%C3%ADsticas-vitales-2022.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>E28</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>INE, Anuario de estadísticas vitales 2023.</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>https://www.ine.gob.cl/docs/default-source/nacimientos-matrimonios-y-defunciones/publicaciones-y-anuarios/anuarios-de-estad%C3%ADsticas-vitales/anuario-de-estad%C3%ADsticas-vitales-2023-nacimientos-y-defunciones.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>E29</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>OPS, perfil de país Chile (indicadores).</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>https://hia.paho.org/en/node/163</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>E30</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Homer et al., Lancet 2014 (Serie Midwifery): efecto proyectado de ampliar la matronería.</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>https://portaldeboaspraticas.iff.fiocruz.br/biblioteca/the-projected-effect-of-scaling-up-midwifery/</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>E31</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Renfrew et al., Lancet 2014: matronería y calidad de la atención.</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>https://portaldeboaspraticas.iff.fiocruz.br/biblioteca/midwifery-and-quality-care-findings-from-a-new-evidence-informed-framework-for-maternal-and-newborn-care/</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>E32</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>ICM: State of the World's Midwifery 2021.</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>https://internationalmidwives.org/?p=2406</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>E33</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Sandall et al., Cochrane 2016: modelos de continuidad liderados por matronas.</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>https://portaldeboaspraticas.iff.fiocruz.br/biblioteca/midwife-led-continuity-models-versus-other-models-of-care-for-childbearing-women/</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>E34</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Winner et al., NEJM 2012 (Proyecto CHOICE): eficacia de LARC.</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>https://read.qxmd.com/read/22621627/effectiveness-of-long-acting-reversible-contraception</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>E35</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Lindo y Packham (UC Davis): acceso a LARC y nacimientos adolescentes en Colorado.</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>https://www.poverty.ucdavis.edu/sites/main/files/file-attachments/cpr-lindo_contraceptive_brief.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>E36</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>OMS, nota descriptiva: educación sexual integral (2026).</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>https://www.who.int/news-room/fact-sheets/detail/comprehensive-sexuality-education</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>E37</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Mason-Jones et al., Cochrane 2016: educación sexual escolar y prevención de VIH, ITS y embarazo.</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>https://www.cochranelibrary.com/cdsr/doi/10.1002/14651858.CD006417.pub3/full</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>E38</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Goldfarb y Lieberman, J Adolesc Health 2021: tres décadas de investigación en educación sexual integral.</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>https://healtheducationresources.unesco.org/library/documents/three-decades-research-case-comprehensive-sex-education</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>E39</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>INJUV, Estudios vol. 12: embarazo adolescente (2020).</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>https://www.injuv.gob.cl/sites/default/files/estudioembarazo.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>E40</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Código Sanitario, artículo 117.</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>https://iura.cl/csan/117</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>E41</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>T13: MINSAL deroga puntos del Decreto 243 tras reunión con el Colegio de Matronas (23-05-2025).</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>https://www.t13.cl/noticia/nacional/minsal-deroga-controvertido-decreto-tras-reunion-colegio-matronas-matrones-23-5-2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>E42</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Pauta: dictamen de Contraloría sobre neonatología (2018).</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>https://www.pauta.cl/actualidad/2018/09/23/la-batalla-entre-matronas-y-enfermeras-por-un-dictamen-de-contraloria.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>E43</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>DOE: Corte Suprema mantiene dictámenes sobre funciones de matronas en neonatología (2026).</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>https://actualidadjuridica.doe.cl/corte-suprema-mantiene-dictamenes-sobre-funciones-de-matronas-en-neonatologia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>E44</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Cámara de Diputados: Comisión de Salud incluye atención de infertilidad en funciones de matronas (20-08-2026).</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>https://www.camara.cl/cms/2026/08/20/comision-de-salud-incluye-en-funciones-de-matronas-atencion-de-infertilidad/</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>E45</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>BioBioChile: urgencia al proyecto de educación sexual integral (07-01-2026).</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>https://www.biobiochile.cl/noticias/nacional/chile/2026/01/07/gobierno-pone-urgencia-a-proyecto-de-educacion-sexual-integral-oposicion-acusa-agenda-ideologica.shtml</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>E46</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Colegio de Matronas: movilización revierte puntos críticos del Decreto 243 (23-05-2025).</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>https://colegiodematronas.cl/2025/05/23/historica-movilizacion-de-la-matroneria-logra-revertir-los-puntos-criticos-del-decreto-243/</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>E47</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Emol: movilización de matronas por la Norma 150 (22-05-2025).</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>https://www.emol.com/noticias/Nacional/2025/05/22/1167011/matronas-movilizacion-norma-150-minsal.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>E48</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Ministerio de Desarrollo Social / Centro de Microdatos U. de Chile: Encuesta Longitudinal de Primera Infancia (ELPI) 2010, informe de resultados.</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>https://bid-ckan.ministeriodesarrollosocial.gob.cl:443/dataset/1b7ab804-2db6-4346-a097-527e5668b113/resource/3151c15f-cb99-4df3-8c18-c4492ef8d974/download/encuesta_elpi_2010.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>E49</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Dussaillant F. Comportamientos riesgosos entre los jóvenes: el caso de la actividad sexual. Estudios Públicos 118, CEP 2010 (datos INJUV 2006 y 2009).</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>https://biblat.unam.mx/hevila/EstudiospublicosSantiago/2010/no118/4.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>E50</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>MINSAL: Situación actual del embarazo adolescente en Chile.</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>https://www.minsal.cl/portal/url/item/c908a2010f2e7dafe040010164010db3.pdf</t>
-        </is>
+      <c r="A12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Opcion</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Orden</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Sí, desde los 14 años</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>No (como hoy en los colegios)</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3292,6 +4889,1392 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Escenario</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Porcentaje</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Orden</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Alto (10%)</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Conservador (5%)</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Puntos</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Orden</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Orden</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Indicador</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Nacimientos 15–19</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>4979</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Embarazo</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Gonorrea</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>2682</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>ITS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Sífilis</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>11155</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>ITS</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Orden</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Supuesto</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>PorQue</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>FuenteID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Colegios con matrona y educación sexual integral</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Lo eliges tú (0% a 100%)</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Qué parte de los colegios tendría una matrona haciendo educación sexual integral</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Supuesto del escenario</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Entrega de anticonceptivos desde los 14 años</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Sí o No</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>La Ley 20.418 garantiza información y acceso a métodos; desde los 14 años la consulta es confidencial</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>E52</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Efecto en los embarazos adolescentes con educación + acceso</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>5% (conservador) o 10% (alto)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>El acceso gratuito a DIU e implantes redujo los nacimientos adolescentes entre 5% y 10% en 4 años</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>E35</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Efecto de la educación sola, sin acceso a métodos</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Los programas escolares sin acceso a anticonceptivos no mostraron un efecto claro en embarazos</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>E37</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Aumento del uso de condón gracias a la educación</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Lo eliges tú (0 a 20 puntos)</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>La educación sexual integral aumenta el uso de condón y anticonceptivos (OMS)</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>E36</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Protección del condón</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>El uso consistente del condón reduce cerca de 80% la transmisión del VIH; se usa como supuesto para las demás ITS</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>E37N</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Datos base</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>4.979 nacimientos de madres de 15 a 19 (2025) · tasa 8,3 por 1.000 · 2.682 casos de gonorrea y 11.155 de sífilis (2025)</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Cifras oficiales del último año disponible</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>FuenteID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Referencia</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MINSAL, Actualización de la situación de salud de adolescentes (2021).</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://diprece.minsal.cl/wp-content/uploads/2021/06/ACTUALIZACION-SITUACION-DE-SALUD-DE-ADOLESCENTES-PROGRAMA-NACIONAL-DE-SALUD-INTEGRAL-DE-ADOLESCENTES-Y-JOVENES.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>INE, Enfoque estadístico maternidad y paternidad (2017).</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.ine.gob.cl/docs/default-source/genero/documentos-de-an%C3%A1lisis/documentos/enfoque-maternidad-paternidad-2017.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>INE vía Emol, cifras de maternidad en Chile (2020).</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.emol.com/noticias/Economia/2020/05/09/985650/Cifras-maternidad-en-Chile.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>INE, nacimientos 2018 (nota de prensa, 2021).</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.ine.gob.cl/sala-de-prensa/prensa/general/noticia/2021/01/11/nacimientos-de-madres-extranjeras-crecen-y-alcanzan-el-14-en-chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>E5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>La Tercera, embarazo adolescente en su cifra más baja (2024).</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.latercera.com/que-pasa/noticia/uso-de-anticonceptivos-llevan-al-embarazo-adolescente-a-la-cifra-mas-baja-desde-que-hay-registros/H5QUT6YRKNH2VDXD7LV6BPYH7Y/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>E6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>INE, Estadísticas vitales: fecundidad en Chile (17-03-2025).</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.ine.gob.cl/sala-de-prensa/prensa/general/noticia/2025/03/17/estad%C3%ADsticas-vitales-fecundidad-en-chile-sigue-bajo-del-nivel-de-reemplazo-generacional</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>E7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>INE, Estadísticas vitales cifras provisionales 2024.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.ine.gob.cl/docs/default-source/nacimientos-matrimonios-y-defunciones/publicaciones-y-anuarios/anuarios-de-estad%C3%ADsticas-vitales/estad%C3%ADsticas-vitales-cifras-provisionales-2024.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>E8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>INE, Estadísticas vitales cifras provisionales 2025.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.ine.gob.cl/docs/default-source/nacimientos-matrimonios-y-defunciones/publicaciones-y-anuarios/anuarios-de-estad%C3%ADsticas-vitales/estad%C3%ADsticas-vitales-cifras-provisionales-2025.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>E9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Intramed: caída del embarazo adolescente en Chile (Rodríguez Vignoli, CEPAL).</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.intramed.net/content/67057bde57fbbb5669b34e22</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>E10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CEPAL, Rodríguez Vignoli: fecundidad adolescente en Chile (datos INJUV 2018).</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://repositorio.cepal.org/server/api/core/bitstreams/6dd4f6c2-3ace-4da3-a9de-b36f1be56c9f/content</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>E11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>La Tercera Paula: 10.ª Encuesta Nacional de Juventudes INJUV 2022.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.latercera.com/paula/mas-tarde-y-las-mujeres-primero-radiografia-al-sexo-adolescente/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>E12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>La Tercera: 50% de los embarazos en Chile no son planificados (encuesta 2010).</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.latercera.com/noticia/50-de-los-embarazos-en-chile-no-son-planificados/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>E13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>UNFPA, State of the World's Midwifery 2021: perfil de Chile.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.unfpa.org/sites/default/files/sowmy21/en/sowmy-2021-profile-cl.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>E14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Guttmacher, embarazo no planeado en América Latina y el Caribe (2022).</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.guttmacher.org/es/infographic/2022/la-tasa-de-embarazo-no-planeado-en-america-latina-y-el-caribe-es-de-69-por-cada</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>E15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>UNFPA, casi la mitad de los embarazos no son intencionales (SWOP 2022).</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.unfpa.org/press/nearly-half-all-pregnancies-are-unintended%E2%80%94-global-crisis-says-new-unfpa-report</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>E16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MINSAL, Glosa 01 letra d: profesionales inscritos en el RNPI (informe 2023).</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.minsal.cl/wp-content/uploads/2021/05/Glosa-01-d-Ano-2023.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>E17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MINSAL, Glosa 01 letra d (informe 2026, datos a diciembre de 2025).</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.minsal.cl/wp-content/uploads/2026/07/Glosa-01-letra-d-comun-a-los-capitulos-inciso-04.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>E18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Clínicas de Chile, Dimensionamiento del sector salud 2022.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.clinicasdechile.cl/wp-content/uploads/2023/12/Dimensionamiento-Completo-2022.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>E19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MINSAL, Normas Nacionales sobre Regulación de la Fertilidad (2018).</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.minsal.cl/wp-content/uploads/2015/09/2018.01.30_NORMAS-REGULACION-DE-LA-FERTILIDAD.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>E20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>UNFPA/OMS/ICM, State of the World's Midwifery 2021.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://unfpa.org/state-worlds-midwifery-2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>E21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MINSAL, Espacios Amigables en Ñuble (2025).</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.minsal.cl/espacios-amigables-se-refuerza-red-de-apoyo-en-salud-para-adolescentes-en-nuble/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>E22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Mortalidad materna Chile 2001–2021 (póster congreso UFRO 2023, datos DEIS).</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://congreso2023.ufro.cl/images/presentaciones/e-poster/viernes/pantalla7/07-797-Tendencias%20de%20Mortalidad%20Materna.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>E23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>González et al., Rev Méd Clín Las Condes 2023: mortalidad materna y prematuridad en pandemia (datos DEIS).</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.elsevier.es/es-revista-revista-medica-clinica-las-condes-202-articulo-aumento-mortalidad-materna-prematuridad-durante-S0716864023000111</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>E24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ORAS-CONHU, Sala situacional de mortalidad materna (estimaciones ONU 2023).</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.orasconhu.org/sites/default/files/file/webfiles/doc/Sala%20Situacional%2014-04-2025%20Mortalidad%20Materna.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>E25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>OMS, nota descriptiva de mortalidad materna.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.who.int/news-room/fact-sheets/detail/maternal-mortality</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>E26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>INE, Anuario de estadísticas vitales 2018 (síntesis).</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.ine.gob.cl/docs/default-source/nacimientos-matrimonios-y-defunciones/publicaciones-y-anuarios/s%C3%ADntesis-anuarios-de-estad%C3%ADsticas-vitales/anuario-de-estad%C3%ADsticas-vitales-2018-s%C3%ADntesis.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>E27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>INE, Anuario de estadísticas vitales 2022.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.ine.gob.cl/docs/default-source/nacimientos-matrimonios-y-defunciones/publicaciones-y-anuarios/anuarios-de-estad%C3%ADsticas-vitales/anuario-de-estad%C3%ADsticas-vitales-2022.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>E28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>INE, Anuario de estadísticas vitales 2023.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://www.ine.gob.cl/docs/default-source/nacimientos-matrimonios-y-defunciones/publicaciones-y-anuarios/anuarios-de-estad%C3%ADsticas-vitales/anuario-de-estad%C3%ADsticas-vitales-2023-nacimientos-y-defunciones.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>E29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>OPS, perfil de país Chile (indicadores).</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://hia.paho.org/en/node/163</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>E30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Homer et al., Lancet 2014 (Serie Midwifery): efecto proyectado de ampliar la matronería.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://portaldeboaspraticas.iff.fiocruz.br/biblioteca/the-projected-effect-of-scaling-up-midwifery/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>E31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Renfrew et al., Lancet 2014: matronería y calidad de la atención.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://portaldeboaspraticas.iff.fiocruz.br/biblioteca/midwifery-and-quality-care-findings-from-a-new-evidence-informed-framework-for-maternal-and-newborn-care/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>E32</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ICM: State of the World's Midwifery 2021.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://internationalmidwives.org/?p=2406</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>E33</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Sandall et al., Cochrane 2016: modelos de continuidad liderados por matronas.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://portaldeboaspraticas.iff.fiocruz.br/biblioteca/midwife-led-continuity-models-versus-other-models-of-care-for-childbearing-women/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>E34</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Winner et al., NEJM 2012 (Proyecto CHOICE): eficacia de LARC.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://read.qxmd.com/read/22621627/effectiveness-of-long-acting-reversible-contraception</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>E35</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Lindo y Packham (UC Davis): acceso a LARC y nacimientos adolescentes en Colorado.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://www.poverty.ucdavis.edu/sites/main/files/file-attachments/cpr-lindo_contraceptive_brief.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>E36</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>OMS, nota descriptiva: educación sexual integral (2026).</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://www.who.int/news-room/fact-sheets/detail/comprehensive-sexuality-education</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>E37</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Mason-Jones et al., Cochrane 2016: educación sexual escolar y prevención de VIH, ITS y embarazo.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://www.cochranelibrary.com/cdsr/doi/10.1002/14651858.CD006417.pub3/full</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>E38</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Goldfarb y Lieberman, J Adolesc Health 2021: tres décadas de investigación en educación sexual integral.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://healtheducationresources.unesco.org/library/documents/three-decades-research-case-comprehensive-sex-education</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>E39</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>INJUV, Estudios vol. 12: embarazo adolescente (2020).</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://www.injuv.gob.cl/sites/default/files/estudioembarazo.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>E40</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Código Sanitario, artículo 117.</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://iura.cl/csan/117</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>E41</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>T13: MINSAL deroga puntos del Decreto 243 tras reunión con el Colegio de Matronas (23-05-2025).</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://www.t13.cl/noticia/nacional/minsal-deroga-controvertido-decreto-tras-reunion-colegio-matronas-matrones-23-5-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>E42</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Pauta: dictamen de Contraloría sobre neonatología (2018).</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://www.pauta.cl/actualidad/2018/09/23/la-batalla-entre-matronas-y-enfermeras-por-un-dictamen-de-contraloria.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>E43</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>DOE: Corte Suprema mantiene dictámenes sobre funciones de matronas en neonatología (2026).</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://actualidadjuridica.doe.cl/corte-suprema-mantiene-dictamenes-sobre-funciones-de-matronas-en-neonatologia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>E44</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Cámara de Diputados: Comisión de Salud incluye atención de infertilidad en funciones de matronas (20-08-2026).</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://www.camara.cl/cms/2026/08/20/comision-de-salud-incluye-en-funciones-de-matronas-atencion-de-infertilidad/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>E45</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BioBioChile: urgencia al proyecto de educación sexual integral (07-01-2026).</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://www.biobiochile.cl/noticias/nacional/chile/2026/01/07/gobierno-pone-urgencia-a-proyecto-de-educacion-sexual-integral-oposicion-acusa-agenda-ideologica.shtml</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>E46</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Colegio de Matronas: movilización revierte puntos críticos del Decreto 243 (23-05-2025).</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://colegiodematronas.cl/2025/05/23/historica-movilizacion-de-la-matroneria-logra-revertir-los-puntos-criticos-del-decreto-243/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>E47</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Emol: movilización de matronas por la Norma 150 (22-05-2025).</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://www.emol.com/noticias/Nacional/2025/05/22/1167011/matronas-movilizacion-norma-150-minsal.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>E48</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Ministerio de Desarrollo Social / Centro de Microdatos U. de Chile: Encuesta Longitudinal de Primera Infancia (ELPI) 2010, informe de resultados.</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://bid-ckan.ministeriodesarrollosocial.gob.cl:443/dataset/1b7ab804-2db6-4346-a097-527e5668b113/resource/3151c15f-cb99-4df3-8c18-c4492ef8d974/download/encuesta_elpi_2010.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>E49</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Dussaillant F. Comportamientos riesgosos entre los jóvenes: el caso de la actividad sexual. Estudios Públicos 118, CEP 2010 (datos INJUV 2006 y 2009).</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://biblat.unam.mx/hevila/EstudiospublicosSantiago/2010/no118/4.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>E50</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>MINSAL: Situación actual del embarazo adolescente en Chile.</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://www.minsal.cl/portal/url/item/c908a2010f2e7dafe040010164010db3.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>E51</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Weller S, Davis K. Condom effectiveness in reducing heterosexual HIV transmission. Cochrane Database Syst Rev 2002 (reducción cercana a 80%).</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/14651858.CD003255</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>E52</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Ley 20.418 (2010): normas sobre información, orientación y prestaciones en materia de regulación de la fertilidad.</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://www.bcn.cl/leychile/navegar?idNorma=1010482</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
